--- a/generated/output.xlsx
+++ b/generated/output.xlsx
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1454</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1064</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3454</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1031</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1078</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1045</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1004</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1044</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1004</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>1487</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12">
@@ -573,7 +573,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>1048</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>1322</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>1054</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>1048</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>1012</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -638,7 +638,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5644</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7494</v>
+        <v>6494</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>1465</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>4145</v>
+        <v>3145</v>
       </c>
     </row>
   </sheetData>
